--- a/data/LBracketMaterials.xlsx
+++ b/data/LBracketMaterials.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\METALS_Clean\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\Personal\suresh\Software\Github\ERSL-Private\METALS\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B7AE57F-8B8E-4281-9100-C349AC4E743A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7D1359D-78C6-4253-BD52-2428ED6E5D7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="25">
   <si>
     <t>Attribute</t>
   </si>
@@ -76,6 +76,24 @@
     <t>Yield_Strength</t>
   </si>
   <si>
+    <t>17-4PH SS</t>
+  </si>
+  <si>
+    <t>Grade 304 SS</t>
+  </si>
+  <si>
+    <t>Nitronic 60</t>
+  </si>
+  <si>
+    <t>7068 Al</t>
+  </si>
+  <si>
+    <t>7075 Al</t>
+  </si>
+  <si>
+    <t>6061 Al</t>
+  </si>
+  <si>
     <t>USD/lb</t>
   </si>
   <si>
@@ -89,15 +107,6 @@
   </si>
   <si>
     <t>Material/Units</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>C</t>
   </si>
 </sst>
 </file>
@@ -113,10 +122,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -127,7 +138,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -136,30 +147,47 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
+      <left style="hair">
+        <color auto="1"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
+      <right style="hair">
+        <color auto="1"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
+      <top style="hair">
+        <color auto="1"/>
       </top>
-      <bottom style="thin">
-        <color indexed="64"/>
+      <bottom style="hair">
+        <color auto="1"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color auto="1"/>
+      </left>
+      <right style="hair">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -442,85 +470,149 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="702" width="20.5703125" customWidth="1"/>
+    <col min="1" max="1" width="20.6640625" style="1" customWidth="1"/>
+    <col min="2" max="702" width="20.5546875" style="1" customWidth="1"/>
+    <col min="703" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="2">
+        <v>7.75</v>
+      </c>
+      <c r="C3" s="2">
+        <v>196</v>
+      </c>
+      <c r="D3" s="2">
+        <v>4</v>
+      </c>
+      <c r="E3" s="2">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="2">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2">
+        <v>193</v>
+      </c>
+      <c r="D4" s="2">
+        <v>2</v>
+      </c>
+      <c r="E4" s="2">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="2">
+        <v>7.62</v>
+      </c>
+      <c r="C5" s="2">
+        <v>181</v>
+      </c>
+      <c r="D5" s="2">
+        <v>2</v>
+      </c>
+      <c r="E5" s="2">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="B6" s="3">
+        <v>2.85</v>
+      </c>
+      <c r="C6" s="3">
+        <v>73</v>
+      </c>
+      <c r="D6" s="3">
+        <v>1</v>
+      </c>
+      <c r="E6" s="3">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="B7" s="3">
+        <v>2.81</v>
+      </c>
+      <c r="C7" s="3">
+        <v>72</v>
+      </c>
+      <c r="D7" s="3">
+        <v>1</v>
+      </c>
+      <c r="E7" s="3">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="2">
-        <v>0.27</v>
-      </c>
-      <c r="C3" s="2">
-        <v>0.6</v>
-      </c>
-      <c r="D3" s="2">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" s="2">
-        <v>0.8</v>
-      </c>
-      <c r="C4" s="2">
-        <v>0.92</v>
-      </c>
-      <c r="D4" s="2">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="2">
+      <c r="B8" s="3">
+        <v>2.7</v>
+      </c>
+      <c r="C8" s="3">
+        <v>69</v>
+      </c>
+      <c r="D8" s="3">
         <v>1</v>
       </c>
-      <c r="C5" s="2">
-        <v>1</v>
-      </c>
-      <c r="D5" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C8" s="1"/>
+      <c r="E8" s="3">
+        <v>276</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -547,12 +639,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECC80EBF-8B96-4896-8C13-AD8A976D05A3}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -566,7 +658,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -580,7 +672,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -594,21 +686,21 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>13</v>
       </c>
